--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,19 +141,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>WXS</t>
+    <t>Whole-Exome-Sequencing</t>
   </si>
   <si>
     <t>Whole Exome Sequencing</t>
   </si>
   <si>
-    <t>WGS</t>
+    <t>Whole-Genome-Sequencing</t>
   </si>
   <si>
     <t>Whole Genome Sequencing</t>
   </si>
   <si>
-    <t>TARS</t>
+    <t>Targeted-Sequencing</t>
   </si>
   <si>
     <t>Targeted Sequencing</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,19 +141,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>Whole-Exome-Sequencing</t>
+    <t>WXS</t>
   </si>
   <si>
     <t>Whole Exome Sequencing</t>
   </si>
   <si>
-    <t>Whole-Genome-Sequencing</t>
+    <t>WGS</t>
   </si>
   <si>
     <t>Whole Genome Sequencing</t>
   </si>
   <si>
-    <t>Targeted-Sequencing</t>
+    <t>TARS</t>
   </si>
   <si>
     <t>Targeted Sequencing</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-experimental-strategy.xlsx
+++ b/docs/CodeSystem-experimental-strategy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>Level</t>
@@ -229,6 +229,18 @@
   </si>
   <si>
     <t>Direct Methyl-Seq</t>
+  </si>
+  <si>
+    <t>ADAS</t>
+  </si>
+  <si>
+    <t>Adaptive Sampling</t>
+  </si>
+  <si>
+    <t>QUES</t>
+  </si>
+  <si>
+    <t>Questionnaire</t>
   </si>
 </sst>
 </file>
@@ -538,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -735,6 +747,30 @@
       </c>
       <c r="D16" s="2"/>
     </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
